--- a/meeple_back/src/main/resources/game-element/bluemarble-tile.xlsx
+++ b/meeple_back/src/main/resources/game-element/bluemarble-tile.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10119"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSAFY\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/biggie/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD6B2840-3CE6-0947-B2C5-446197E50A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15300" windowHeight="6860"/>
+    <workbookView xWindow="17180" yWindow="6280" windowWidth="25260" windowHeight="18700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="63">
   <si>
     <t>id</t>
   </si>
@@ -222,54 +223,53 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>백조자리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>헬리혜성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>헬리혜성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yellow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yellow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>뉴런의골짜기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>백조자리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>헬리혜성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>헬리혜성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>yellow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>금성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>yellow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -476,7 +476,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -753,11 +753,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E41"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -774,7 +774,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>0</v>
       </c>
@@ -787,7 +787,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -804,7 +804,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -817,7 +817,7 @@
       </c>
       <c r="E4" s="8"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -834,7 +834,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -851,7 +851,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -868,7 +868,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -885,7 +885,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -898,7 +898,7 @@
       </c>
       <c r="E9" s="8"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -915,7 +915,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -932,7 +932,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>10</v>
       </c>
@@ -940,10 +940,12 @@
         <v>20</v>
       </c>
       <c r="C12" s="6"/>
-      <c r="D12" s="7"/>
+      <c r="D12" s="7" t="s">
+        <v>20</v>
+      </c>
       <c r="E12" s="8"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>11</v>
       </c>
@@ -960,7 +962,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>12</v>
       </c>
@@ -977,7 +979,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>13</v>
       </c>
@@ -990,7 +992,7 @@
       </c>
       <c r="E15" s="8"/>
     </row>
-    <row r="16" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>14</v>
       </c>
@@ -1007,7 +1009,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>15</v>
       </c>
@@ -1015,10 +1017,12 @@
         <v>25</v>
       </c>
       <c r="C17" s="6"/>
-      <c r="D17" s="7"/>
+      <c r="D17" s="7" t="s">
+        <v>62</v>
+      </c>
       <c r="E17" s="8"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>16</v>
       </c>
@@ -1035,7 +1039,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <v>17</v>
       </c>
@@ -1052,7 +1056,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>18</v>
       </c>
@@ -1069,7 +1073,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <v>19</v>
       </c>
@@ -1086,7 +1090,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>20</v>
       </c>
@@ -1099,7 +1103,7 @@
       </c>
       <c r="E22" s="8"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>21</v>
       </c>
@@ -1116,7 +1120,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>22</v>
       </c>
@@ -1133,7 +1137,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>23</v>
       </c>
@@ -1141,10 +1145,12 @@
         <v>10</v>
       </c>
       <c r="C25" s="6"/>
-      <c r="D25" s="7"/>
+      <c r="D25" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="E25" s="8"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>24</v>
       </c>
@@ -1161,7 +1167,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>25</v>
       </c>
@@ -1178,7 +1184,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>26</v>
       </c>
@@ -1195,7 +1201,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>27</v>
       </c>
@@ -1212,7 +1218,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>28</v>
       </c>
@@ -1229,7 +1235,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>29</v>
       </c>
@@ -1238,11 +1244,11 @@
       </c>
       <c r="C31" s="6"/>
       <c r="D31" s="7" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
         <v>30</v>
       </c>
@@ -1255,7 +1261,7 @@
       </c>
       <c r="E32" s="8"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
         <v>31</v>
       </c>
@@ -1272,7 +1278,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A34" s="5">
         <v>32</v>
       </c>
@@ -1289,7 +1295,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
         <v>33</v>
       </c>
@@ -1297,10 +1303,12 @@
         <v>45</v>
       </c>
       <c r="C35" s="6"/>
-      <c r="D35" s="7"/>
+      <c r="D35" s="7" t="s">
+        <v>17</v>
+      </c>
       <c r="E35" s="8"/>
     </row>
-    <row r="36" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
         <v>34</v>
       </c>
@@ -1317,7 +1325,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:5" ht="48" x14ac:dyDescent="0.2">
       <c r="A37" s="5">
         <v>35</v>
       </c>
@@ -1326,16 +1334,16 @@
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="7" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="E37" s="8"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
         <v>36</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>51</v>
@@ -1347,28 +1355,28 @@
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
         <v>37</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E39" s="8"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="5">
         <v>38</v>
       </c>
       <c r="B40" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>12</v>
@@ -1377,15 +1385,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>39</v>
       </c>
       <c r="B41" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C41" s="10" t="s">
         <v>61</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>62</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>52</v>
@@ -1395,7 +1403,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E41"/>
+  <autoFilter ref="A1:E41" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/meeple_back/src/main/resources/game-element/bluemarble-tile.xlsx
+++ b/meeple_back/src/main/resources/game-element/bluemarble-tile.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/biggie/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD6B2840-3CE6-0947-B2C5-446197E50A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A093C4-4F0E-884B-B100-50A7D0DD80D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17180" yWindow="6280" windowWidth="25260" windowHeight="18700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32360" yWindow="6620" windowWidth="25260" windowHeight="18700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -283,7 +283,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -370,15 +370,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -413,17 +404,6 @@
       </right>
       <top/>
       <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -434,7 +414,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -466,13 +446,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -783,9 +757,6 @@
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="8">
-        <v>20</v>
-      </c>
     </row>
     <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
@@ -800,8 +771,8 @@
       <c r="D3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="8">
-        <v>10</v>
+      <c r="E3">
+        <v>100000</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -815,7 +786,6 @@
       <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="8"/>
     </row>
     <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
@@ -830,8 +800,8 @@
       <c r="D5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="8">
-        <v>15</v>
+      <c r="E5">
+        <v>150000</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -847,8 +817,8 @@
       <c r="D6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="8">
-        <v>30</v>
+      <c r="E6">
+        <v>300000</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -864,8 +834,8 @@
       <c r="D7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="8">
-        <v>50</v>
+      <c r="E7">
+        <v>500000</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -881,8 +851,8 @@
       <c r="D8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="8">
-        <v>30</v>
+      <c r="E8">
+        <v>300000</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -896,7 +866,6 @@
       <c r="D9" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
@@ -911,8 +880,8 @@
       <c r="D10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="8">
-        <v>15</v>
+      <c r="E10">
+        <v>150000</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -928,8 +897,8 @@
       <c r="D11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="8">
-        <v>15</v>
+      <c r="E11">
+        <v>150000</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -943,7 +912,6 @@
       <c r="D12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="8"/>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
@@ -958,8 +926,8 @@
       <c r="D13" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="8">
-        <v>25</v>
+      <c r="E13">
+        <v>250000</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -975,8 +943,8 @@
       <c r="D14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="8">
-        <v>30</v>
+      <c r="E14">
+        <v>300000</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -990,7 +958,6 @@
       <c r="D15" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E15" s="8"/>
     </row>
     <row r="16" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
@@ -1005,8 +972,8 @@
       <c r="D16" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="8">
-        <v>40</v>
+      <c r="E16">
+        <v>400000</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="48" x14ac:dyDescent="0.2">
@@ -1020,7 +987,6 @@
       <c r="D17" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="8"/>
     </row>
     <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
@@ -1035,8 +1001,8 @@
       <c r="D18" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="8">
-        <v>45</v>
+      <c r="E18">
+        <v>450000</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1052,8 +1018,8 @@
       <c r="D19" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="8">
-        <v>50</v>
+      <c r="E19">
+        <v>500000</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1069,8 +1035,8 @@
       <c r="D20" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="8">
-        <v>50</v>
+      <c r="E20">
+        <v>500000</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1086,8 +1052,8 @@
       <c r="D21" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="8">
-        <v>60</v>
+      <c r="E21">
+        <v>600000</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1101,7 +1067,6 @@
       <c r="D22" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="8"/>
     </row>
     <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
@@ -1116,8 +1081,8 @@
       <c r="D23" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="8">
-        <v>60</v>
+      <c r="E23">
+        <v>600000</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1133,8 +1098,8 @@
       <c r="D24" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="8">
-        <v>50</v>
+      <c r="E24">
+        <v>500000</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1148,7 +1113,6 @@
       <c r="D25" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E25" s="8"/>
     </row>
     <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
@@ -1163,8 +1127,8 @@
       <c r="D26" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="8">
-        <v>45</v>
+      <c r="E26">
+        <v>450000</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1180,8 +1144,8 @@
       <c r="D27" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="8">
-        <v>50</v>
+      <c r="E27">
+        <v>500000</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1197,8 +1161,8 @@
       <c r="D28" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E28" s="8">
-        <v>40</v>
+      <c r="E28">
+        <v>400000</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1214,8 +1178,8 @@
       <c r="D29" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E29" s="8">
-        <v>30</v>
+      <c r="E29">
+        <v>300000</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1231,8 +1195,8 @@
       <c r="D30" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E30" s="8">
-        <v>25</v>
+      <c r="E30">
+        <v>250000</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1246,7 +1210,6 @@
       <c r="D31" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E31" s="8"/>
     </row>
     <row r="32" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
@@ -1259,7 +1222,6 @@
       <c r="D32" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E32" s="8"/>
     </row>
     <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
@@ -1274,8 +1236,8 @@
       <c r="D33" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="8">
-        <v>30</v>
+      <c r="E33">
+        <v>300000</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1291,8 +1253,8 @@
       <c r="D34" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="8">
-        <v>40</v>
+      <c r="E34">
+        <v>400000</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="32" x14ac:dyDescent="0.2">
@@ -1306,7 +1268,6 @@
       <c r="D35" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E35" s="8"/>
     </row>
     <row r="36" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
@@ -1321,8 +1282,8 @@
       <c r="D36" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E36" s="8">
-        <v>40</v>
+      <c r="E36">
+        <v>400000</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="48" x14ac:dyDescent="0.2">
@@ -1336,7 +1297,6 @@
       <c r="D37" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="8"/>
     </row>
     <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
@@ -1351,8 +1311,8 @@
       <c r="D38" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E38" s="8">
-        <v>30</v>
+      <c r="E38">
+        <v>300000</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
@@ -1366,7 +1326,6 @@
       <c r="D39" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E39" s="8"/>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="5">
@@ -1381,25 +1340,25 @@
       <c r="D40" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E40" s="8">
-        <v>10</v>
+      <c r="E40">
+        <v>100000</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="9">
+      <c r="A41" s="8">
         <v>39</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="E41" s="12">
-        <v>10</v>
+      <c r="E41">
+        <v>100000</v>
       </c>
     </row>
   </sheetData>

--- a/meeple_back/src/main/resources/game-element/bluemarble-tile.xlsx
+++ b/meeple_back/src/main/resources/game-element/bluemarble-tile.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/biggie/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A093C4-4F0E-884B-B100-50A7D0DD80D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C49D6B5-9DC2-FF45-9ECC-DF1A3151F914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32360" yWindow="6620" windowWidth="25260" windowHeight="18700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2120" yWindow="4320" windowWidth="40960" windowHeight="25600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$41</definedName>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="102">
   <si>
     <t>id</t>
   </si>
@@ -252,13 +253,130 @@
   </si>
   <si>
     <t>뉴런의골짜기</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/earth.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/moon.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/telepathy.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/mars.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/jupiter.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/vega.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/saturn.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/uranus.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/neptune.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/timetravel.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/aries.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/taurus.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/telepathy2.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/gemini.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/neurons1.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/cancer.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/timemachine.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/leo.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/virgo.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/blackhole.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/libra.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/scorpio.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/telepathy3.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/sagittarius.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/altair.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/capricorn.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/aquarius.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/pisces.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/resquebase.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/ursamajor.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/andromeda.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/telepathy4.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/orion.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/neurons2.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/cygnus.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/halley.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/mercury.png</t>
+  </si>
+  <si>
+    <t>https://meeple-file-server-2.s3.ap-northeast-2.amazonaws.com/bluemable/venus.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -269,6 +387,15 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="129"/>
@@ -409,12 +536,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -448,8 +578,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -728,10 +865,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="6" max="6" width="73.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -747,8 +887,11 @@
       <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F1" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="5">
         <v>0</v>
       </c>
@@ -757,8 +900,11 @@
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
-    </row>
-    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -774,8 +920,11 @@
       <c r="E3">
         <v>100000</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="F3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>2</v>
       </c>
@@ -786,8 +935,11 @@
       <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>3</v>
       </c>
@@ -803,8 +955,11 @@
       <c r="E5">
         <v>150000</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>4</v>
       </c>
@@ -820,8 +975,11 @@
       <c r="E6">
         <v>300000</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="5">
         <v>5</v>
       </c>
@@ -837,8 +995,11 @@
       <c r="E7">
         <v>500000</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="5">
         <v>6</v>
       </c>
@@ -854,8 +1015,11 @@
       <c r="E8">
         <v>300000</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="F8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="5">
         <v>7</v>
       </c>
@@ -866,8 +1030,11 @@
       <c r="D9" s="7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F9" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -883,8 +1050,11 @@
       <c r="E10">
         <v>150000</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F10" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="5">
         <v>9</v>
       </c>
@@ -900,8 +1070,11 @@
       <c r="E11">
         <v>150000</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="5">
         <v>10</v>
       </c>
@@ -912,8 +1085,11 @@
       <c r="D12" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="5">
         <v>11</v>
       </c>
@@ -929,8 +1105,11 @@
       <c r="E13">
         <v>250000</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="5">
         <v>12</v>
       </c>
@@ -946,8 +1125,11 @@
       <c r="E14">
         <v>300000</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="F14" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="5">
         <v>13</v>
       </c>
@@ -958,8 +1140,11 @@
       <c r="D15" s="7" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="F15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="5">
         <v>14</v>
       </c>
@@ -975,8 +1160,11 @@
       <c r="E16">
         <v>400000</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="F16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A17" s="5">
         <v>15</v>
       </c>
@@ -987,8 +1175,11 @@
       <c r="D17" s="7" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="5">
         <v>16</v>
       </c>
@@ -1004,8 +1195,11 @@
       <c r="E18">
         <v>450000</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F18" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="5">
         <v>17</v>
       </c>
@@ -1021,8 +1215,11 @@
       <c r="E19">
         <v>500000</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F19" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="5">
         <v>18</v>
       </c>
@@ -1038,8 +1235,11 @@
       <c r="E20">
         <v>500000</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="5">
         <v>19</v>
       </c>
@@ -1055,8 +1255,11 @@
       <c r="E21">
         <v>600000</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="5">
         <v>20</v>
       </c>
@@ -1067,8 +1270,11 @@
       <c r="D22" s="7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="5">
         <v>21</v>
       </c>
@@ -1084,8 +1290,11 @@
       <c r="E23">
         <v>600000</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F23" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="5">
         <v>22</v>
       </c>
@@ -1101,8 +1310,11 @@
       <c r="E24">
         <v>500000</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="F24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>23</v>
       </c>
@@ -1113,8 +1325,11 @@
       <c r="D25" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>24</v>
       </c>
@@ -1130,8 +1345,11 @@
       <c r="E26">
         <v>450000</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F26" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>25</v>
       </c>
@@ -1147,8 +1365,11 @@
       <c r="E27">
         <v>500000</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F27" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>26</v>
       </c>
@@ -1164,8 +1385,11 @@
       <c r="E28">
         <v>400000</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F28" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>27</v>
       </c>
@@ -1181,8 +1405,11 @@
       <c r="E29">
         <v>300000</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="F29" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>28</v>
       </c>
@@ -1198,8 +1425,11 @@
       <c r="E30">
         <v>250000</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="F30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>29</v>
       </c>
@@ -1210,8 +1440,11 @@
       <c r="D31" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="F31" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
         <v>30</v>
       </c>
@@ -1222,8 +1455,11 @@
       <c r="D32" s="7" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F32" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
         <v>31</v>
       </c>
@@ -1239,8 +1475,11 @@
       <c r="E33">
         <v>300000</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="F33" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A34" s="5">
         <v>32</v>
       </c>
@@ -1256,8 +1495,11 @@
       <c r="E34">
         <v>400000</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="F34" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
         <v>33</v>
       </c>
@@ -1268,8 +1510,11 @@
       <c r="D35" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="F35" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
         <v>34</v>
       </c>
@@ -1285,8 +1530,11 @@
       <c r="E36">
         <v>400000</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="F36" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A37" s="5">
         <v>35</v>
       </c>
@@ -1297,8 +1545,11 @@
       <c r="D37" s="7" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F37" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="5">
         <v>36</v>
       </c>
@@ -1314,8 +1565,11 @@
       <c r="E38">
         <v>300000</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F38" s="12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="5">
         <v>37</v>
       </c>
@@ -1326,8 +1580,11 @@
       <c r="D39" s="7" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+      <c r="F39" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="5">
         <v>38</v>
       </c>
@@ -1343,8 +1600,11 @@
       <c r="E40">
         <v>100000</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F40" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8">
         <v>39</v>
       </c>
@@ -1359,11 +1619,27 @@
       </c>
       <c r="E41">
         <v>100000</v>
+      </c>
+      <c r="F41" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:E41" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F9" r:id="rId1" xr:uid="{46BDEF0D-3C8B-7B46-9E46-9A0823837424}"/>
+    <hyperlink ref="F38" r:id="rId2" xr:uid="{9AB75343-7606-504F-A3A1-8B97755ED9A6}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DEB57EF-409F-A64E-A507-FB90CD717676}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>